--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/coalitions.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/coalitions.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t xml:space="preserve">majority_sorted</t>
   </si>
@@ -27,6 +27,12 @@
     <t xml:space="preserve">case</t>
   </si>
   <si>
+    <t xml:space="preserve">Roberts, Alito, Thomas, Kagan, Gorsuch, Kavanaugh, Barrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lackey; Advocate Christ Medical</t>
+  </si>
+  <si>
     <t xml:space="preserve">Roberts, Alito, Thomas, Sotomayor, Kagan, Kavanaugh, Barrett</t>
   </si>
   <si>
@@ -51,16 +57,16 @@
     <t xml:space="preserve">Trump v. J.G.G.</t>
   </si>
   <si>
-    <t xml:space="preserve">Roberts, Alito, Thomas, Kagan, Gorsuch, Kavanaugh, Barrett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lackey</t>
-  </si>
-  <si>
     <t xml:space="preserve">Roberts, Alito, Thomas, Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
   </si>
   <si>
     <t xml:space="preserve">Miller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts, Sotomayor, Gorsuch, Kavanaugh, Barrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feliciano</t>
   </si>
   <si>
     <t xml:space="preserve">Roberts, Sotomayor, Kagan, Gorsuch, Jackson</t>
@@ -506,7 +512,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -609,6 +615,17 @@
       </c>
       <c r="C12" t="s">
         <v>24</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -624,7 +641,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -632,7 +649,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B2" t="n">
         <v>28</v>
@@ -640,7 +657,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B3" t="n">
         <v>31</v>
@@ -648,7 +665,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B4" t="n">
         <v>31</v>
@@ -656,7 +673,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B5" t="n">
         <v>20</v>
@@ -664,7 +681,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B6" t="n">
         <v>30</v>
@@ -672,7 +689,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B7" t="n">
         <v>27</v>
@@ -680,7 +697,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B8" t="n">
         <v>18</v>
@@ -688,7 +705,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B9" t="n">
         <v>26</v>
@@ -696,7 +713,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B10" t="n">
         <v>31</v>
@@ -704,7 +721,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B11" t="n">
         <v>19</v>
@@ -712,7 +729,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B12" t="n">
         <v>24</v>
@@ -720,7 +737,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B13" t="n">
         <v>31</v>
@@ -728,7 +745,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B14" t="n">
         <v>18</v>
@@ -736,7 +753,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B15" t="n">
         <v>26</v>
@@ -744,18 +761,18 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B17" t="n">
-        <v>24.4</v>
+        <v>24.4666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -771,15 +788,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B2" t="n">
         <v>33</v>
@@ -787,7 +804,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B3" t="n">
         <v>40</v>
@@ -795,7 +812,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B4" t="n">
         <v>39</v>
@@ -803,7 +820,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B5" t="n">
         <v>27</v>
@@ -811,7 +828,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B6" t="n">
         <v>41</v>
@@ -819,7 +836,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B7" t="n">
         <v>33</v>
@@ -827,7 +844,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B8" t="n">
         <v>26</v>
@@ -835,7 +852,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B9" t="n">
         <v>34</v>
@@ -843,7 +860,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B10" t="n">
         <v>42</v>
@@ -851,7 +868,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B11" t="n">
         <v>32</v>
@@ -859,7 +876,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B12" t="n">
         <v>37</v>
@@ -867,7 +884,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B13" t="n">
         <v>48</v>
@@ -875,7 +892,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B14" t="n">
         <v>31</v>
@@ -883,7 +900,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B15" t="n">
         <v>44</v>
@@ -891,18 +908,18 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B16" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B17" t="n">
-        <v>35.2666666666667</v>
+        <v>35.4</v>
       </c>
     </row>
   </sheetData>
@@ -918,15 +935,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -934,7 +951,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B3" t="n">
         <v>6</v>
@@ -942,7 +959,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -950,7 +967,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B5" t="n">
         <v>5</v>
@@ -958,7 +975,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B6" t="n">
         <v>5</v>
@@ -966,7 +983,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
@@ -974,7 +991,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B8" t="n">
         <v>4</v>
@@ -982,7 +999,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B9" t="n">
         <v>19</v>
@@ -990,7 +1007,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B10" t="n">
         <v>10</v>
@@ -998,7 +1015,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B11" t="n">
         <v>13</v>
@@ -1006,7 +1023,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B12" t="n">
         <v>18</v>
@@ -1014,7 +1031,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B13" t="n">
         <v>28</v>
@@ -1022,7 +1039,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B14" t="n">
         <v>12</v>
@@ -1030,7 +1047,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B15" t="n">
         <v>22</v>
@@ -1038,7 +1055,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B16" t="n">
         <v>0</v>
@@ -1046,7 +1063,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B17" t="n">
         <v>11.4</v>
@@ -1065,15 +1082,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B2" t="n">
         <v>29</v>
@@ -1081,7 +1098,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B3" t="n">
         <v>29</v>
@@ -1089,7 +1106,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B4" t="n">
         <v>24</v>
@@ -1097,7 +1114,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B5" t="n">
         <v>23</v>
@@ -1105,7 +1122,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B6" t="n">
         <v>26</v>
@@ -1113,7 +1130,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B7" t="n">
         <v>26</v>
@@ -1121,7 +1138,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B8" t="n">
         <v>20</v>
@@ -1129,7 +1146,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B9" t="n">
         <v>22</v>
@@ -1137,7 +1154,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B10" t="n">
         <v>28</v>
@@ -1145,7 +1162,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B11" t="n">
         <v>21</v>
@@ -1153,7 +1170,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B12" t="n">
         <v>24</v>
@@ -1161,7 +1178,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B13" t="n">
         <v>20</v>
@@ -1169,7 +1186,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B14" t="n">
         <v>21</v>
@@ -1177,7 +1194,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B15" t="n">
         <v>20</v>
@@ -1185,15 +1202,15 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B17" t="n">
         <v>23.5</v>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/coalitions.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/coalitions.xlsx
@@ -1,170 +1,177 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaketruscott\Github\scotuswatch\Stat Reviews\OT24_StatReview\scotusblog_replication\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55D337F4-5BB2-434D-9720-BBD023A6F64D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="ot24_coalitions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="all_splits" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="perc_split_of_total_cases" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="perc_ideological_splits" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="unique_coalitions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ot24_coalitions" sheetId="1" r:id="rId1"/>
+    <sheet name="all_splits" sheetId="2" r:id="rId2"/>
+    <sheet name="perc_split_of_total_cases" sheetId="3" r:id="rId3"/>
+    <sheet name="perc_ideological_splits" sheetId="4" r:id="rId4"/>
+    <sheet name="unique_coalitions" sheetId="5" r:id="rId5"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
-  <si>
-    <t xml:space="preserve">majority_sorted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">case</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts, Alito, Thomas, Kagan, Gorsuch, Kavanaugh, Barrett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lackey; Advocate Christ Medical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts, Alito, Thomas, Sotomayor, Kagan, Kavanaugh, Barrett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bufkin; Delligatti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alito, Thomas, Gorsuch, Kavanaugh, Barrett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOE v. CA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts, Alito, Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andrew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts, Alito, Thomas, Gorsuch, Kavanaugh, Barrett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trump v. J.G.G.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts, Alito, Thomas, Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts, Sotomayor, Gorsuch, Kavanaugh, Barrett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feliciano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts, Sotomayor, Kagan, Gorsuch, Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Velazquez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts, Sotomayor, Kagan, Gorsuch, Kavanaugh, Barrett, Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vanderstok</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts, Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glossip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts, Sotomayor, Kagan, Kavanaugh, Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Willaims</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sotomayor, Kagan, Gorsuch, Barrett, Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medical Marijuana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">term</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Average</t>
-  </si>
-  <si>
-    <t xml:space="preserve">percent_split</t>
-  </si>
-  <si>
-    <t xml:space="preserve">percent_ideological_split</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unique_coalitions</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="47">
+  <si>
+    <t>majority_sorted</t>
+  </si>
+  <si>
+    <t>count</t>
+  </si>
+  <si>
+    <t>case</t>
+  </si>
+  <si>
+    <t>Roberts, Alito, Thomas, Kagan, Gorsuch, Kavanaugh, Barrett</t>
+  </si>
+  <si>
+    <t>Lackey; Advocate Christ Medical</t>
+  </si>
+  <si>
+    <t>Roberts, Alito, Thomas, Sotomayor, Kagan, Kavanaugh, Barrett</t>
+  </si>
+  <si>
+    <t>Bufkin; Delligatti</t>
+  </si>
+  <si>
+    <t>Alito, Thomas, Gorsuch, Kavanaugh, Barrett</t>
+  </si>
+  <si>
+    <t>DOE v. CA</t>
+  </si>
+  <si>
+    <t>Roberts, Alito, Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
+  </si>
+  <si>
+    <t>Andrew</t>
+  </si>
+  <si>
+    <t>Roberts, Alito, Thomas, Gorsuch, Kavanaugh, Barrett</t>
+  </si>
+  <si>
+    <t>Trump v. J.G.G.</t>
+  </si>
+  <si>
+    <t>Roberts, Alito, Thomas, Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
+  </si>
+  <si>
+    <t>Miller</t>
+  </si>
+  <si>
+    <t>Roberts, Sotomayor, Gorsuch, Kavanaugh, Barrett</t>
+  </si>
+  <si>
+    <t>Feliciano</t>
+  </si>
+  <si>
+    <t>Roberts, Sotomayor, Kagan, Gorsuch, Jackson</t>
+  </si>
+  <si>
+    <t>Velazquez</t>
+  </si>
+  <si>
+    <t>Roberts, Sotomayor, Kagan, Gorsuch, Kavanaugh, Barrett, Jackson</t>
+  </si>
+  <si>
+    <t>Vanderstok</t>
+  </si>
+  <si>
+    <t>Roberts, Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
+  </si>
+  <si>
+    <t>Glossip</t>
+  </si>
+  <si>
+    <t>Roberts, Sotomayor, Kagan, Kavanaugh, Jackson</t>
+  </si>
+  <si>
+    <t>Willaims</t>
+  </si>
+  <si>
+    <t>Sotomayor, Kagan, Gorsuch, Barrett, Jackson</t>
+  </si>
+  <si>
+    <t>Medical Marijuana</t>
+  </si>
+  <si>
+    <t>term</t>
+  </si>
+  <si>
+    <t>2010</t>
+  </si>
+  <si>
+    <t>2011</t>
+  </si>
+  <si>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>2013</t>
+  </si>
+  <si>
+    <t>2014</t>
+  </si>
+  <si>
+    <t>2015</t>
+  </si>
+  <si>
+    <t>2016</t>
+  </si>
+  <si>
+    <t>2017</t>
+  </si>
+  <si>
+    <t>2018</t>
+  </si>
+  <si>
+    <t>2019</t>
+  </si>
+  <si>
+    <t>2020</t>
+  </si>
+  <si>
+    <t>2021</t>
+  </si>
+  <si>
+    <t>2022</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>percent_split</t>
+  </si>
+  <si>
+    <t>percent_ideological_split</t>
+  </si>
+  <si>
+    <t>unique_coalitions</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -200,6 +207,15 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -481,11 +497,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -496,132 +512,132 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>2</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>2</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>11</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>13</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>15</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>17</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>1</v>
       </c>
       <c r="C10" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>21</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>1</v>
       </c>
       <c r="C11" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>23</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>25</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="s">
@@ -630,16 +646,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>27</v>
       </c>
@@ -647,146 +663,146 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>28</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>28</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>29</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>31</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>30</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>31</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>31</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>20</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>32</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>30</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>33</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>27</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>34</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>18</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>35</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>26</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>36</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>31</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>37</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>19</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>38</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>24</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>39</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>31</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>40</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>18</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>41</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>26</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>42</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>7</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>43</v>
       </c>
-      <c r="B17" t="n">
-        <v>24.4666666666667</v>
+      <c r="B17">
+        <v>24.466666666666701</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>27</v>
       </c>
@@ -794,146 +810,146 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>28</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>33</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>29</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>40</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>30</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>39</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>31</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>27</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>32</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>41</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>33</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>33</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>34</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>26</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>35</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>34</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>36</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>42</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>37</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>32</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>38</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>37</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>39</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>48</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>40</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>31</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>41</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>44</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>42</v>
       </c>
-      <c r="B16" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17">
+      <c r="B16">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>43</v>
       </c>
-      <c r="B17" t="n">
-        <v>35.4</v>
+      <c r="B17">
+        <v>35.3333333333333</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>27</v>
       </c>
@@ -941,146 +957,146 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>28</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>14</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>29</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>6</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>30</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>14</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>31</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>5</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>32</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>5</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>33</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>1</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>34</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>4</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>35</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>19</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>36</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>10</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>37</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>13</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>38</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>18</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>39</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>28</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>40</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>12</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>41</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>22</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>42</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>0</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>43</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>11.4</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>27</v>
       </c>
@@ -1088,136 +1104,136 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>28</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>29</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>29</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>29</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>30</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>24</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>31</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>23</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>32</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>26</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>33</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>26</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>34</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>20</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>35</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>22</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>36</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>28</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>37</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>21</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>38</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>24</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>39</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>20</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>40</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>21</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>41</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>20</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>42</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>12</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>43</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>23.5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/coalitions.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/coalitions.xlsx
@@ -1,177 +1,210 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaketruscott\Github\scotuswatch\Stat Reviews\OT24_StatReview\scotusblog_replication\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55D337F4-5BB2-434D-9720-BBD023A6F64D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="ot24_coalitions" sheetId="1" r:id="rId1"/>
-    <sheet name="all_splits" sheetId="2" r:id="rId2"/>
-    <sheet name="perc_split_of_total_cases" sheetId="3" r:id="rId3"/>
-    <sheet name="perc_ideological_splits" sheetId="4" r:id="rId4"/>
-    <sheet name="unique_coalitions" sheetId="5" r:id="rId5"/>
+    <sheet name="ot24_coalitions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="all_splits" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="perc_split_of_total_cases" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="perc_ideological_splits" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="unique_coalitions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="conservative_defections" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="47">
-  <si>
-    <t>majority_sorted</t>
-  </si>
-  <si>
-    <t>count</t>
-  </si>
-  <si>
-    <t>case</t>
-  </si>
-  <si>
-    <t>Roberts, Alito, Thomas, Kagan, Gorsuch, Kavanaugh, Barrett</t>
-  </si>
-  <si>
-    <t>Lackey; Advocate Christ Medical</t>
-  </si>
-  <si>
-    <t>Roberts, Alito, Thomas, Sotomayor, Kagan, Kavanaugh, Barrett</t>
-  </si>
-  <si>
-    <t>Bufkin; Delligatti</t>
-  </si>
-  <si>
-    <t>Alito, Thomas, Gorsuch, Kavanaugh, Barrett</t>
-  </si>
-  <si>
-    <t>DOE v. CA</t>
-  </si>
-  <si>
-    <t>Roberts, Alito, Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
-  </si>
-  <si>
-    <t>Andrew</t>
-  </si>
-  <si>
-    <t>Roberts, Alito, Thomas, Gorsuch, Kavanaugh, Barrett</t>
-  </si>
-  <si>
-    <t>Trump v. J.G.G.</t>
-  </si>
-  <si>
-    <t>Roberts, Alito, Thomas, Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
-  </si>
-  <si>
-    <t>Miller</t>
-  </si>
-  <si>
-    <t>Roberts, Sotomayor, Gorsuch, Kavanaugh, Barrett</t>
-  </si>
-  <si>
-    <t>Feliciano</t>
-  </si>
-  <si>
-    <t>Roberts, Sotomayor, Kagan, Gorsuch, Jackson</t>
-  </si>
-  <si>
-    <t>Velazquez</t>
-  </si>
-  <si>
-    <t>Roberts, Sotomayor, Kagan, Gorsuch, Kavanaugh, Barrett, Jackson</t>
-  </si>
-  <si>
-    <t>Vanderstok</t>
-  </si>
-  <si>
-    <t>Roberts, Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
-  </si>
-  <si>
-    <t>Glossip</t>
-  </si>
-  <si>
-    <t>Roberts, Sotomayor, Kagan, Kavanaugh, Jackson</t>
-  </si>
-  <si>
-    <t>Willaims</t>
-  </si>
-  <si>
-    <t>Sotomayor, Kagan, Gorsuch, Barrett, Jackson</t>
-  </si>
-  <si>
-    <t>Medical Marijuana</t>
-  </si>
-  <si>
-    <t>term</t>
-  </si>
-  <si>
-    <t>2010</t>
-  </si>
-  <si>
-    <t>2011</t>
-  </si>
-  <si>
-    <t>2012</t>
-  </si>
-  <si>
-    <t>2013</t>
-  </si>
-  <si>
-    <t>2014</t>
-  </si>
-  <si>
-    <t>2015</t>
-  </si>
-  <si>
-    <t>2016</t>
-  </si>
-  <si>
-    <t>2017</t>
-  </si>
-  <si>
-    <t>2018</t>
-  </si>
-  <si>
-    <t>2019</t>
-  </si>
-  <si>
-    <t>2020</t>
-  </si>
-  <si>
-    <t>2021</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>2023</t>
-  </si>
-  <si>
-    <t>2024</t>
-  </si>
-  <si>
-    <t>Average</t>
-  </si>
-  <si>
-    <t>percent_split</t>
-  </si>
-  <si>
-    <t>percent_ideological_split</t>
-  </si>
-  <si>
-    <t>unique_coalitions</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+  <si>
+    <t xml:space="preserve">majority_sorted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts, Alito, Thomas, Kagan, Gorsuch, Kavanaugh, Barrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lackey; Advocate Christ Medical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts, Alito, Thomas, Sotomayor, Kagan, Kavanaugh, Barrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bufkin; Delligatti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts, Sotomayor, Kagan, Gorsuch, Kavanaugh, Barrett, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vanderstok; A.A.R.P v. Trump</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito, Thomas, Gorsuch, Kavanaugh, Barrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOE v. CA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts, Alito, Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andrew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts, Alito, Thomas, Gorsuch, Kavanaugh, Barrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump v. J.G.G.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts, Alito, Thomas, Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miller</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts, Sotomayor, Gorsuch, Kavanaugh, Barrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feliciano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts, Sotomayor, Kagan, Gorsuch, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Velazquez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts, Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glossip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts, Sotomayor, Kagan, Kavanaugh, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Willaims</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sotomayor, Kagan, Gorsuch, Barrett, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medical Marijuana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">term</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average</t>
+  </si>
+  <si>
+    <t xml:space="preserve">percent_split</t>
+  </si>
+  <si>
+    <t xml:space="preserve">percent_ideological_split</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique_coalitions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">justice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_defections</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_cases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">percent_defection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorsuch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kavanaugh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -207,15 +240,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -497,11 +521,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -512,132 +536,132 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>2</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="n">
         <v>2</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4">
-        <v>1</v>
+      <c r="B4" t="n">
+        <v>2</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>11</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>13</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>15</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>17</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>19</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>21</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
         <v>23</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
         <v>25</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="s">
@@ -646,16 +670,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>27</v>
       </c>
@@ -663,146 +687,146 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>28</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>29</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>30</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>31</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>32</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>33</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="n">
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>34</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>35</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>36</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>37</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="n">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
         <v>38</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="n">
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
         <v>39</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" t="s">
         <v>40</v>
       </c>
-      <c r="B14">
+      <c r="B14" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" t="s">
         <v>41</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" t="s">
         <v>42</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" t="s">
         <v>43</v>
       </c>
-      <c r="B17">
-        <v>24.466666666666701</v>
+      <c r="B17" t="n">
+        <v>24.4666666666667</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>27</v>
       </c>
@@ -810,146 +834,146 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>28</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>29</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>30</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="n">
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>31</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="n">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>32</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="n">
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>33</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="n">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>34</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>35</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="n">
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>36</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="n">
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>37</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="n">
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
         <v>38</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="n">
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
         <v>39</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="n">
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" t="s">
         <v>40</v>
       </c>
-      <c r="B14">
+      <c r="B14" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" t="s">
         <v>41</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="n">
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" t="s">
         <v>42</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="n">
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" t="s">
         <v>43</v>
       </c>
-      <c r="B17">
+      <c r="B17" t="n">
         <v>35.3333333333333</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>27</v>
       </c>
@@ -957,146 +981,146 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>28</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>29</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>30</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>31</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>32</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>33</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>34</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>35</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="n">
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>36</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>37</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
         <v>38</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
         <v>39</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="n">
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" t="s">
         <v>40</v>
       </c>
-      <c r="B14">
+      <c r="B14" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" t="s">
         <v>41</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" t="s">
         <v>42</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" t="s">
         <v>43</v>
       </c>
-      <c r="B17">
+      <c r="B17" t="n">
         <v>11.4</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>27</v>
       </c>
@@ -1104,136 +1128,351 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>28</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>29</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>30</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="n">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>31</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="n">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>32</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>33</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>34</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>35</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>36</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="n">
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>37</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
         <v>38</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="n">
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
         <v>39</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" t="s">
         <v>40</v>
       </c>
-      <c r="B14">
+      <c r="B14" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" t="s">
         <v>41</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" t="s">
         <v>42</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" t="s">
         <v>43</v>
       </c>
-      <c r="B17">
+      <c r="B17" t="n">
         <v>23.5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D2" t="n">
+        <v>158</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>158</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" t="n">
+        <v>47</v>
+      </c>
+      <c r="D4" t="n">
+        <v>158</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="n">
+        <v>158</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" t="n">
+        <v>37</v>
+      </c>
+      <c r="D6" t="n">
+        <v>158</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" t="n">
+        <v>18</v>
+      </c>
+      <c r="D7" t="n">
+        <v>158</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" t="n">
+        <v>58</v>
+      </c>
+      <c r="D8" t="n">
+        <v>158</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" t="n">
+        <v>59</v>
+      </c>
+      <c r="D9" t="n">
+        <v>158</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>158</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C11" t="n">
+        <v>19</v>
+      </c>
+      <c r="D11" t="n">
+        <v>158</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" t="n">
+        <v>11</v>
+      </c>
+      <c r="D12" t="n">
+        <v>158</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.07</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/coalitions.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/coalitions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaketruscott\Github\scotuswatch\Stat Reviews\OT24_StatReview\scotusblog_replication\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26AA79BC-AB4E-4DB1-921E-F5619A473EFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E0077AD-B40C-40D9-BC2F-60EDA41148A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31065" yWindow="2055" windowWidth="21570" windowHeight="11295" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ot24_coalitions" sheetId="1" r:id="rId1"/>
@@ -1001,7 +1001,7 @@
         <v>46</v>
       </c>
       <c r="B16">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -1009,7 +1009,7 @@
         <v>47</v>
       </c>
       <c r="B17">
-        <v>35.200000000000003</v>
+        <v>34.933333333333302</v>
       </c>
     </row>
   </sheetData>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/coalitions.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/coalitions.xlsx
@@ -1,229 +1,234 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jaketruscott\Github\scotuswatch\Stat Reviews\OT24_StatReview\scotusblog_replication\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E0077AD-B40C-40D9-BC2F-60EDA41148A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="ot24_coalitions" sheetId="1" r:id="rId1"/>
-    <sheet name="all_splits" sheetId="2" r:id="rId2"/>
-    <sheet name="perc_split_of_total_cases" sheetId="3" r:id="rId3"/>
-    <sheet name="perc_ideological_splits" sheetId="4" r:id="rId4"/>
-    <sheet name="unique_coalitions" sheetId="5" r:id="rId5"/>
-    <sheet name="conservative_defections" sheetId="6" r:id="rId6"/>
+    <sheet name="ot24_coalitions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="all_splits" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="perc_split_of_total_cases" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="perc_ideological_splits" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="unique_coalitions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="conservative_defections" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="64">
-  <si>
-    <t>majority_sorted</t>
-  </si>
-  <si>
-    <t>count</t>
-  </si>
-  <si>
-    <t>case</t>
-  </si>
-  <si>
-    <t>Roberts, Alito, Thomas, Kagan, Gorsuch, Kavanaugh, Barrett</t>
-  </si>
-  <si>
-    <t>Lackey; Advocate Christ Medical</t>
-  </si>
-  <si>
-    <t>Roberts, Alito, Thomas, Sotomayor, Kagan, Kavanaugh, Barrett</t>
-  </si>
-  <si>
-    <t>Bufkin; Delligatti</t>
-  </si>
-  <si>
-    <t>Roberts, Sotomayor, Kagan, Gorsuch, Kavanaugh, Barrett, Jackson</t>
-  </si>
-  <si>
-    <t>Vanderstok; A.A.R.P v. Trump</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Drummond</t>
-  </si>
-  <si>
-    <t>Alito, Thomas, Gorsuch, Kavanaugh, Barrett</t>
-  </si>
-  <si>
-    <t>DOE v. CA</t>
-  </si>
-  <si>
-    <t>Roberts, Alito, Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
-  </si>
-  <si>
-    <t>Andrew</t>
-  </si>
-  <si>
-    <t>Roberts, Alito, Thomas, Gorsuch, Kavanaugh, Barrett</t>
-  </si>
-  <si>
-    <t>Trump v. J.G.G.</t>
-  </si>
-  <si>
-    <t>Roberts, Alito, Thomas, Sotomayor, Kagan, Gorsuch, Kavanaugh, Barrett, Jackson</t>
-  </si>
-  <si>
-    <t>Seven County</t>
-  </si>
-  <si>
-    <t>Roberts, Alito, Thomas, Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
-  </si>
-  <si>
-    <t>Miller</t>
-  </si>
-  <si>
-    <t>Roberts, Sotomayor, Gorsuch, Kavanaugh, Barrett</t>
-  </si>
-  <si>
-    <t>Feliciano</t>
-  </si>
-  <si>
-    <t>Roberts, Sotomayor, Kagan, Gorsuch, Jackson</t>
-  </si>
-  <si>
-    <t>Velazquez</t>
-  </si>
-  <si>
-    <t>Roberts, Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
-  </si>
-  <si>
-    <t>Glossip</t>
-  </si>
-  <si>
-    <t>Roberts, Sotomayor, Kagan, Kavanaugh, Jackson</t>
-  </si>
-  <si>
-    <t>Willaims</t>
-  </si>
-  <si>
-    <t>Sotomayor, Kagan, Gorsuch, Barrett, Jackson</t>
-  </si>
-  <si>
-    <t>Medical Marijuana</t>
-  </si>
-  <si>
-    <t>term</t>
-  </si>
-  <si>
-    <t>2010</t>
-  </si>
-  <si>
-    <t>2011</t>
-  </si>
-  <si>
-    <t>2012</t>
-  </si>
-  <si>
-    <t>2013</t>
-  </si>
-  <si>
-    <t>2014</t>
-  </si>
-  <si>
-    <t>2015</t>
-  </si>
-  <si>
-    <t>2016</t>
-  </si>
-  <si>
-    <t>2017</t>
-  </si>
-  <si>
-    <t>2018</t>
-  </si>
-  <si>
-    <t>2019</t>
-  </si>
-  <si>
-    <t>2020</t>
-  </si>
-  <si>
-    <t>2021</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>2023</t>
-  </si>
-  <si>
-    <t>2024</t>
-  </si>
-  <si>
-    <t>Average</t>
-  </si>
-  <si>
-    <t>percent_split</t>
-  </si>
-  <si>
-    <t>percent_ideological_split</t>
-  </si>
-  <si>
-    <t>unique_coalitions</t>
-  </si>
-  <si>
-    <t>justice</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>total_defections</t>
-  </si>
-  <si>
-    <t>total_cases</t>
-  </si>
-  <si>
-    <t>percent_defection</t>
-  </si>
-  <si>
-    <t>Alito</t>
-  </si>
-  <si>
-    <t>M1</t>
-  </si>
-  <si>
-    <t>M2</t>
-  </si>
-  <si>
-    <t>Barrett</t>
-  </si>
-  <si>
-    <t>Gorsuch</t>
-  </si>
-  <si>
-    <t>Kavanaugh</t>
-  </si>
-  <si>
-    <t>Roberts</t>
-  </si>
-  <si>
-    <t>Thomas</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+  <si>
+    <t xml:space="preserve">majority_sorted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts, Alito, Thomas, Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miller; Parrish; Zuch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts, Alito, Thomas, Kagan, Gorsuch, Kavanaugh, Barrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lackey; Advocate Christ Medical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts, Alito, Thomas, Sotomayor, Kagan, Kavanaugh, Barrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bufkin; Delligatti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts, Sotomayor, Kagan, Gorsuch, Kavanaugh, Barrett, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vanderstok; A.A.R.P v. Trump</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Drummond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito, Thomas, Gorsuch, Kavanaugh, Barrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOE v. CA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts, Alito, Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andrew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts, Alito, Thomas, Gorsuch, Kavanaugh, Barrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump v. J.G.G.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts, Alito, Thomas, Sotomayor, Kagan, Gorsuch, Kavanaugh, Barrett, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seven County</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts, Sotomayor, Gorsuch, Kavanaugh, Barrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feliciano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts, Sotomayor, Kagan, Gorsuch, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Velazquez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts, Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glossip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts, Sotomayor, Kagan, Kavanaugh, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Willaims</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sotomayor, Kagan, Gorsuch, Barrett, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medical Marijuana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">term</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average</t>
+  </si>
+  <si>
+    <t xml:space="preserve">percent_split</t>
+  </si>
+  <si>
+    <t xml:space="preserve">percent_ideological_split</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unique_coalitions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">justice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_defections</t>
+  </si>
+  <si>
+    <t xml:space="preserve">total_cases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">percent_defection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Breyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gorsuch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kagan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kavanaugh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sotomayor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thomas</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -259,15 +264,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -549,11 +545,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -564,154 +560,154 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2">
-        <v>2</v>
+      <c r="B2" t="n">
+        <v>3</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="n">
         <v>2</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="n">
         <v>2</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="B5">
-        <v>1</v>
+      <c r="B5" t="n">
+        <v>2</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>11</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>13</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>15</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>17</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>19</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="n">
         <v>1</v>
       </c>
       <c r="C10" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>21</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="n">
         <v>1</v>
       </c>
       <c r="C11" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
         <v>23</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="n">
         <v>1</v>
       </c>
       <c r="C12" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
         <v>25</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" t="s">
         <v>27</v>
       </c>
-      <c r="B14">
+      <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" t="s">
         <v>29</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="s">
@@ -720,16 +716,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>31</v>
       </c>
@@ -737,146 +733,146 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>32</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>33</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>34</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>35</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>36</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>37</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="n">
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>38</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>39</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>40</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>41</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="n">
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
         <v>42</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="n">
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
         <v>43</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" t="s">
         <v>44</v>
       </c>
-      <c r="B14">
+      <c r="B14" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" t="s">
         <v>45</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" t="s">
         <v>46</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" t="s">
         <v>47</v>
       </c>
-      <c r="B17">
-        <v>24.466666666666701</v>
+      <c r="B17" t="n">
+        <v>24.4666666666667</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>31</v>
       </c>
@@ -884,146 +880,146 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>32</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>33</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="n">
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>34</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="n">
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>35</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="n">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>36</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="n">
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>37</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="n">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>38</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>39</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="n">
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>40</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="n">
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>41</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="n">
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
         <v>42</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="n">
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
         <v>43</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="n">
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" t="s">
         <v>44</v>
       </c>
-      <c r="B14">
+      <c r="B14" t="n">
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" t="s">
         <v>45</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="n">
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" t="s">
         <v>46</v>
       </c>
-      <c r="B16">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B16" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" t="s">
         <v>47</v>
       </c>
-      <c r="B17">
-        <v>34.933333333333302</v>
+      <c r="B17" t="n">
+        <v>34.8</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>31</v>
       </c>
@@ -1031,146 +1027,146 @@
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>32</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>33</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>34</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>35</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>36</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>37</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>38</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>39</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="n">
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>40</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>41</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
         <v>42</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
         <v>43</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="n">
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" t="s">
         <v>44</v>
       </c>
-      <c r="B14">
+      <c r="B14" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" t="s">
         <v>45</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" t="s">
         <v>46</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" t="s">
         <v>47</v>
       </c>
-      <c r="B17">
+      <c r="B17" t="n">
         <v>11.4</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>31</v>
       </c>
@@ -1178,146 +1174,146 @@
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>32</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>33</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="n">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>34</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="n">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>35</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="n">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>36</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>37</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>38</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>39</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>40</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="n">
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>41</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
         <v>42</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="n">
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
         <v>43</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" t="s">
         <v>44</v>
       </c>
-      <c r="B14">
+      <c r="B14" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" t="s">
         <v>45</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="n">
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" t="s">
         <v>46</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" t="s">
         <v>47</v>
       </c>
-      <c r="B17">
+      <c r="B17" t="n">
         <v>23.5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>51</v>
       </c>
@@ -1334,195 +1330,331 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>56</v>
       </c>
       <c r="B2" t="s">
         <v>57</v>
       </c>
-      <c r="C2">
-        <v>21</v>
-      </c>
-      <c r="D2">
-        <v>160</v>
-      </c>
-      <c r="E2">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C2" t="n">
+        <v>22</v>
+      </c>
+      <c r="D2" t="n">
+        <v>160</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
         <v>56</v>
       </c>
       <c r="B3" t="s">
         <v>58</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>3</v>
       </c>
-      <c r="D3">
-        <v>160</v>
-      </c>
-      <c r="E3">
+      <c r="D3" t="n">
+        <v>160</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.02</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>59</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>48</v>
       </c>
-      <c r="D4">
-        <v>160</v>
-      </c>
-      <c r="E4">
+      <c r="D4" t="n">
+        <v>160</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>59</v>
       </c>
       <c r="B5" t="s">
         <v>58</v>
       </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-      <c r="D5">
-        <v>160</v>
-      </c>
-      <c r="E5">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>160</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
         <v>60</v>
       </c>
       <c r="B6" t="s">
         <v>57</v>
       </c>
-      <c r="C6">
-        <v>38</v>
-      </c>
-      <c r="D6">
-        <v>160</v>
-      </c>
-      <c r="E6">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C6" t="n">
+        <v>13</v>
+      </c>
+      <c r="D6" t="n">
+        <v>160</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="s">
         <v>60</v>
       </c>
       <c r="B7" t="s">
         <v>58</v>
       </c>
-      <c r="C7">
-        <v>18</v>
-      </c>
-      <c r="D7">
-        <v>160</v>
-      </c>
-      <c r="E7">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>160</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="s">
         <v>61</v>
       </c>
       <c r="B8" t="s">
         <v>57</v>
       </c>
-      <c r="C8">
-        <v>59</v>
-      </c>
-      <c r="D8">
-        <v>160</v>
-      </c>
-      <c r="E8">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C8" t="n">
+        <v>37</v>
+      </c>
+      <c r="D8" t="n">
+        <v>160</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
-      </c>
-      <c r="C9">
-        <v>60</v>
-      </c>
-      <c r="D9">
-        <v>160</v>
-      </c>
-      <c r="E9">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+      <c r="C9" t="n">
+        <v>20</v>
+      </c>
+      <c r="D9" t="n">
+        <v>160</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="s">
         <v>62</v>
       </c>
       <c r="B10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" t="n">
+        <v>7</v>
+      </c>
+      <c r="D10" t="n">
+        <v>160</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" t="s">
         <v>58</v>
       </c>
-      <c r="C10">
+      <c r="C11" t="n">
         <v>4</v>
       </c>
-      <c r="D10">
-        <v>160</v>
-      </c>
-      <c r="E10">
+      <c r="D11" t="n">
+        <v>160</v>
+      </c>
+      <c r="E11" t="n">
         <v>0.03</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>63</v>
-      </c>
-      <c r="B11" t="s">
-        <v>57</v>
-      </c>
-      <c r="C11">
-        <v>20</v>
-      </c>
-      <c r="D11">
-        <v>160</v>
-      </c>
-      <c r="E11">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
         <v>63</v>
       </c>
       <c r="B12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" t="n">
+        <v>23</v>
+      </c>
+      <c r="D12" t="n">
+        <v>160</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" t="s">
         <v>58</v>
       </c>
-      <c r="C12">
-        <v>11</v>
-      </c>
-      <c r="D12">
-        <v>160</v>
-      </c>
-      <c r="E12">
-        <v>7.0000000000000007E-2</v>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>160</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" t="n">
+        <v>60</v>
+      </c>
+      <c r="D14" t="n">
+        <v>160</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" t="n">
+        <v>61</v>
+      </c>
+      <c r="D15" t="n">
+        <v>160</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" t="n">
+        <v>160</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>66</v>
+      </c>
+      <c r="B17" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" t="n">
+        <v>14</v>
+      </c>
+      <c r="D17" t="n">
+        <v>160</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>66</v>
+      </c>
+      <c r="B18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" t="n">
+        <v>7</v>
+      </c>
+      <c r="D18" t="n">
+        <v>160</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" t="n">
+        <v>21</v>
+      </c>
+      <c r="D19" t="n">
+        <v>160</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" t="n">
+        <v>13</v>
+      </c>
+      <c r="D20" t="n">
+        <v>160</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.08</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/coalitions.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/coalitions.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
   <si>
     <t xml:space="preserve">majority_sorted</t>
   </si>
@@ -28,30 +28,48 @@
     <t xml:space="preserve">case</t>
   </si>
   <si>
+    <t xml:space="preserve">Roberts, Alito, Thomas, Kagan, Gorsuch, Kavanaugh, Barrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lackey; Advocate Christ Medical; Diamond;  R.J. Reynolds </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts, Alito, Thomas, Gorsuch, Kavanaugh, Barrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trump v. J.G.G.; Skrmetti; McLaughlin</t>
+  </si>
+  <si>
     <t xml:space="preserve">Roberts, Alito, Thomas, Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
   </si>
   <si>
     <t xml:space="preserve">Miller; Parrish; Zuch</t>
   </si>
   <si>
-    <t xml:space="preserve">Roberts, Alito, Thomas, Kagan, Gorsuch, Kavanaugh, Barrett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lackey; Advocate Christ Medical</t>
-  </si>
-  <si>
     <t xml:space="preserve">Roberts, Alito, Thomas, Sotomayor, Kagan, Kavanaugh, Barrett</t>
   </si>
   <si>
     <t xml:space="preserve">Bufkin; Delligatti</t>
   </si>
   <si>
+    <t xml:space="preserve">Roberts, Sotomayor, Kagan, Gorsuch, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Velazquez; Perttu</t>
+  </si>
+  <si>
     <t xml:space="preserve">Roberts, Sotomayor, Kagan, Gorsuch, Kavanaugh, Barrett, Jackson</t>
   </si>
   <si>
     <t xml:space="preserve">Vanderstok; A.A.R.P v. Trump</t>
   </si>
   <si>
+    <t xml:space="preserve">Roberts, Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glossip; NRC</t>
+  </si>
+  <si>
     <t xml:space="preserve"/>
   </si>
   <si>
@@ -64,16 +82,22 @@
     <t xml:space="preserve">DOE v. CA</t>
   </si>
   <si>
+    <t xml:space="preserve">Alito, Thomas, Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calumet </t>
+  </si>
+  <si>
     <t xml:space="preserve">Roberts, Alito, Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
   </si>
   <si>
     <t xml:space="preserve">Andrew</t>
   </si>
   <si>
-    <t xml:space="preserve">Roberts, Alito, Thomas, Gorsuch, Kavanaugh, Barrett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trump v. J.G.G.</t>
+    <t xml:space="preserve">Roberts, Alito, Thomas, Sotomayor, Kagan, Gorsuch, Kavanaugh, Barrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stanley</t>
   </si>
   <si>
     <t xml:space="preserve">Roberts, Alito, Thomas, Sotomayor, Kagan, Gorsuch, Kavanaugh, Barrett, Jackson</t>
@@ -88,22 +112,22 @@
     <t xml:space="preserve">Feliciano</t>
   </si>
   <si>
-    <t xml:space="preserve">Roberts, Sotomayor, Kagan, Gorsuch, Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Velazquez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts, Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glossip</t>
-  </si>
-  <si>
     <t xml:space="preserve">Roberts, Sotomayor, Kagan, Kavanaugh, Jackson</t>
   </si>
   <si>
     <t xml:space="preserve">Willaims</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts, Thomas, Sotomayor, Kagan, Gorsuch, Kavanaugh, Barrett, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oklahoma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts, Thomas, Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Esteras</t>
   </si>
   <si>
     <t xml:space="preserve">Sotomayor, Kagan, Gorsuch, Barrett, Jackson</t>
@@ -565,7 +589,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -576,7 +600,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -587,7 +611,7 @@
         <v>7</v>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
@@ -609,7 +633,7 @@
         <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="s">
         <v>12</v>
@@ -620,7 +644,7 @@
         <v>13</v>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
@@ -631,7 +655,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="s">
         <v>16</v>
@@ -712,6 +736,50 @@
       </c>
       <c r="C15" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -727,7 +795,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -735,7 +803,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B2" t="n">
         <v>28</v>
@@ -743,7 +811,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B3" t="n">
         <v>31</v>
@@ -751,7 +819,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B4" t="n">
         <v>31</v>
@@ -759,7 +827,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="B5" t="n">
         <v>20</v>
@@ -767,7 +835,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B6" t="n">
         <v>30</v>
@@ -775,7 +843,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B7" t="n">
         <v>27</v>
@@ -783,7 +851,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B8" t="n">
         <v>18</v>
@@ -791,7 +859,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B9" t="n">
         <v>26</v>
@@ -799,7 +867,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B10" t="n">
         <v>31</v>
@@ -807,7 +875,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="B11" t="n">
         <v>19</v>
@@ -815,7 +883,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B12" t="n">
         <v>24</v>
@@ -823,7 +891,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B13" t="n">
         <v>31</v>
@@ -831,7 +899,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B14" t="n">
         <v>18</v>
@@ -839,7 +907,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B15" t="n">
         <v>26</v>
@@ -847,18 +915,18 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B16" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B17" t="n">
-        <v>24.4666666666667</v>
+        <v>24.7333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -874,15 +942,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B1" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B2" t="n">
         <v>33</v>
@@ -890,7 +958,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B3" t="n">
         <v>40</v>
@@ -898,7 +966,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B4" t="n">
         <v>39</v>
@@ -906,7 +974,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="B5" t="n">
         <v>27</v>
@@ -914,7 +982,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B6" t="n">
         <v>41</v>
@@ -922,7 +990,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B7" t="n">
         <v>33</v>
@@ -930,7 +998,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B8" t="n">
         <v>26</v>
@@ -938,7 +1006,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B9" t="n">
         <v>34</v>
@@ -946,7 +1014,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B10" t="n">
         <v>42</v>
@@ -954,7 +1022,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="B11" t="n">
         <v>32</v>
@@ -962,7 +1030,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B12" t="n">
         <v>37</v>
@@ -970,7 +1038,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B13" t="n">
         <v>48</v>
@@ -978,7 +1046,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B14" t="n">
         <v>31</v>
@@ -986,7 +1054,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B15" t="n">
         <v>44</v>
@@ -994,18 +1062,18 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B17" t="n">
-        <v>34.8</v>
+        <v>35.0666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -1021,15 +1089,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -1037,7 +1105,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B3" t="n">
         <v>6</v>
@@ -1045,7 +1113,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -1053,7 +1121,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="B5" t="n">
         <v>5</v>
@@ -1061,7 +1129,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B6" t="n">
         <v>5</v>
@@ -1069,7 +1137,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
@@ -1077,7 +1145,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B8" t="n">
         <v>4</v>
@@ -1085,7 +1153,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B9" t="n">
         <v>19</v>
@@ -1093,7 +1161,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B10" t="n">
         <v>10</v>
@@ -1101,7 +1169,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="B11" t="n">
         <v>13</v>
@@ -1109,7 +1177,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B12" t="n">
         <v>18</v>
@@ -1117,7 +1185,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B13" t="n">
         <v>28</v>
@@ -1125,7 +1193,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B14" t="n">
         <v>12</v>
@@ -1133,7 +1201,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B15" t="n">
         <v>22</v>
@@ -1141,18 +1209,50 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B17" t="n">
-        <v>11.4</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>54</v>
+      </c>
+      <c r="B18" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" t="n">
+        <v>9.31578947368421</v>
       </c>
     </row>
   </sheetData>
@@ -1168,15 +1268,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B2" t="n">
         <v>29</v>
@@ -1184,7 +1284,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B3" t="n">
         <v>29</v>
@@ -1192,7 +1292,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B4" t="n">
         <v>24</v>
@@ -1200,7 +1300,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="B5" t="n">
         <v>23</v>
@@ -1208,7 +1308,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B6" t="n">
         <v>26</v>
@@ -1216,7 +1316,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B7" t="n">
         <v>26</v>
@@ -1224,7 +1324,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B8" t="n">
         <v>20</v>
@@ -1232,7 +1332,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B9" t="n">
         <v>22</v>
@@ -1240,7 +1340,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B10" t="n">
         <v>28</v>
@@ -1248,7 +1348,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="B11" t="n">
         <v>21</v>
@@ -1256,7 +1356,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B12" t="n">
         <v>24</v>
@@ -1264,7 +1364,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="B13" t="n">
         <v>20</v>
@@ -1272,7 +1372,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="B14" t="n">
         <v>21</v>
@@ -1280,7 +1380,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="B15" t="n">
         <v>20</v>
@@ -1288,15 +1388,15 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B17" t="n">
         <v>23.5</v>
@@ -1315,186 +1415,186 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="B1" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C1" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D1" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E1" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="E2" t="n">
-        <v>0.14</v>
+        <v>0.136</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C3" t="n">
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C4" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D4" t="n">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3</v>
+        <v>0.302</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C6" t="n">
         <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="E6" t="n">
-        <v>0.08</v>
+        <v>0.077</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C7" t="n">
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D8" t="n">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="E8" t="n">
-        <v>0.23</v>
+        <v>0.225</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C9" t="n">
         <v>20</v>
       </c>
       <c r="D9" t="n">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="E9" t="n">
-        <v>0.12</v>
+        <v>0.118</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C10" t="n">
         <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="E10" t="n">
-        <v>0.04</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="B11" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="E11" t="n">
         <v>0.03</v>
@@ -1502,155 +1602,155 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="E12" t="n">
-        <v>0.14</v>
+        <v>0.154</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="B13" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C13" t="n">
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="E13" t="n">
-        <v>0.02</v>
+        <v>0.018</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="B14" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C14" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="E14" t="n">
-        <v>0.38</v>
+        <v>0.373</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B15" t="s">
         <v>65</v>
       </c>
-      <c r="B15" t="s">
-        <v>57</v>
-      </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="E15" t="n">
-        <v>0.38</v>
+        <v>0.379</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B16" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C16" t="n">
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="E16" t="n">
-        <v>0.03</v>
+        <v>0.024</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D17" t="n">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="E17" t="n">
-        <v>0.09</v>
+        <v>0.089</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" t="s">
         <v>66</v>
-      </c>
-      <c r="B18" t="s">
-        <v>58</v>
       </c>
       <c r="C18" t="n">
         <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="E18" t="n">
-        <v>0.04</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C19" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D19" t="n">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="E19" t="n">
-        <v>0.13</v>
+        <v>0.136</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C20" t="n">
         <v>13</v>
       </c>
       <c r="D20" t="n">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="E20" t="n">
-        <v>0.08</v>
+        <v>0.077</v>
       </c>
     </row>
   </sheetData>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/coalitions.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/coalitions.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
   <si>
     <t xml:space="preserve">majority_sorted</t>
   </si>
@@ -221,9 +221,6 @@
   </si>
   <si>
     <t xml:space="preserve">Barrett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Breyer</t>
   </si>
   <si>
     <t xml:space="preserve">Gorsuch</t>
@@ -1444,7 +1441,7 @@
         <v>169</v>
       </c>
       <c r="E2" t="n">
-        <v>0.136</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="3">
@@ -1461,7 +1458,7 @@
         <v>169</v>
       </c>
       <c r="E3" t="n">
-        <v>0.018</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="4">
@@ -1478,7 +1475,7 @@
         <v>169</v>
       </c>
       <c r="E4" t="n">
-        <v>0.302</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="5">
@@ -1495,7 +1492,7 @@
         <v>169</v>
       </c>
       <c r="E5" t="n">
-        <v>0.018</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="6">
@@ -1506,13 +1503,13 @@
         <v>65</v>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="D6" t="n">
         <v>169</v>
       </c>
       <c r="E6" t="n">
-        <v>0.077</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="7">
@@ -1523,13 +1520,13 @@
         <v>66</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D7" t="n">
         <v>169</v>
       </c>
       <c r="E7" t="n">
-        <v>0.012</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="8">
@@ -1540,13 +1537,13 @@
         <v>65</v>
       </c>
       <c r="C8" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
         <v>169</v>
       </c>
       <c r="E8" t="n">
-        <v>0.225</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="9">
@@ -1557,13 +1554,13 @@
         <v>66</v>
       </c>
       <c r="C9" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
         <v>169</v>
       </c>
       <c r="E9" t="n">
-        <v>0.118</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="10">
@@ -1574,13 +1571,13 @@
         <v>65</v>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
         <v>169</v>
       </c>
       <c r="E10" t="n">
-        <v>0.041</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="11">
@@ -1591,13 +1588,13 @@
         <v>66</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
         <v>169</v>
       </c>
       <c r="E11" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="12">
@@ -1608,30 +1605,30 @@
         <v>65</v>
       </c>
       <c r="C12" t="n">
-        <v>26</v>
+        <v>63</v>
       </c>
       <c r="D12" t="n">
         <v>169</v>
       </c>
       <c r="E12" t="n">
-        <v>0.154</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
         <v>169</v>
       </c>
       <c r="E13" t="n">
-        <v>0.018</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="14">
@@ -1639,16 +1636,16 @@
         <v>72</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
         <v>169</v>
       </c>
       <c r="E14" t="n">
-        <v>0.373</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="15">
@@ -1659,13 +1656,13 @@
         <v>65</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>15</v>
       </c>
       <c r="D15" t="n">
         <v>169</v>
       </c>
       <c r="E15" t="n">
-        <v>0.379</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="16">
@@ -1676,13 +1673,13 @@
         <v>66</v>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>169</v>
       </c>
       <c r="E16" t="n">
-        <v>0.024</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="17">
@@ -1693,13 +1690,13 @@
         <v>65</v>
       </c>
       <c r="C17" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D17" t="n">
         <v>169</v>
       </c>
       <c r="E17" t="n">
-        <v>0.089</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="18">
@@ -1710,47 +1707,13 @@
         <v>66</v>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D18" t="n">
         <v>169</v>
       </c>
       <c r="E18" t="n">
-        <v>0.041</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>75</v>
-      </c>
-      <c r="B19" t="s">
-        <v>65</v>
-      </c>
-      <c r="C19" t="n">
-        <v>23</v>
-      </c>
-      <c r="D19" t="n">
-        <v>169</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.136</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>75</v>
-      </c>
-      <c r="B20" t="s">
-        <v>66</v>
-      </c>
-      <c r="C20" t="n">
-        <v>13</v>
-      </c>
-      <c r="D20" t="n">
-        <v>169</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.077</v>
+        <v>0.08</v>
       </c>
     </row>
   </sheetData>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/coalitions.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/coalitions.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
   <si>
     <t xml:space="preserve">majority_sorted</t>
   </si>
@@ -92,6 +92,12 @@
   </si>
   <si>
     <t xml:space="preserve">Andrew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts, Alito, Thomas, Sotomayor, Kagan, Gorsuch, Barrett, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laboratory Corp.</t>
   </si>
   <si>
     <t xml:space="preserve">Roberts, Alito, Thomas, Sotomayor, Kagan, Gorsuch, Kavanaugh, Barrett</t>
@@ -779,6 +785,17 @@
         <v>38</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -792,7 +809,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -800,7 +817,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B2" t="n">
         <v>28</v>
@@ -808,7 +825,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B3" t="n">
         <v>31</v>
@@ -816,7 +833,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B4" t="n">
         <v>31</v>
@@ -824,7 +841,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B5" t="n">
         <v>20</v>
@@ -832,7 +849,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B6" t="n">
         <v>30</v>
@@ -840,7 +857,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B7" t="n">
         <v>27</v>
@@ -848,7 +865,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B8" t="n">
         <v>18</v>
@@ -856,7 +873,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B9" t="n">
         <v>26</v>
@@ -864,7 +881,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B10" t="n">
         <v>31</v>
@@ -872,7 +889,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B11" t="n">
         <v>19</v>
@@ -880,7 +897,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B12" t="n">
         <v>24</v>
@@ -888,7 +905,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B13" t="n">
         <v>31</v>
@@ -896,7 +913,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B14" t="n">
         <v>18</v>
@@ -904,7 +921,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B15" t="n">
         <v>26</v>
@@ -912,7 +929,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B16" t="n">
         <v>11</v>
@@ -920,7 +937,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B17" t="n">
         <v>24.7333333333333</v>
@@ -939,15 +956,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B2" t="n">
         <v>33</v>
@@ -955,7 +972,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B3" t="n">
         <v>40</v>
@@ -963,7 +980,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B4" t="n">
         <v>39</v>
@@ -971,7 +988,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B5" t="n">
         <v>27</v>
@@ -979,7 +996,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B6" t="n">
         <v>41</v>
@@ -987,7 +1004,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B7" t="n">
         <v>33</v>
@@ -995,7 +1012,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B8" t="n">
         <v>26</v>
@@ -1003,7 +1020,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B9" t="n">
         <v>34</v>
@@ -1011,7 +1028,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B10" t="n">
         <v>42</v>
@@ -1019,7 +1036,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B11" t="n">
         <v>32</v>
@@ -1027,7 +1044,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B12" t="n">
         <v>37</v>
@@ -1035,7 +1052,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B13" t="n">
         <v>48</v>
@@ -1043,7 +1060,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B14" t="n">
         <v>31</v>
@@ -1051,7 +1068,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B15" t="n">
         <v>44</v>
@@ -1059,7 +1076,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B16" t="n">
         <v>19</v>
@@ -1067,7 +1084,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B17" t="n">
         <v>35.0666666666667</v>
@@ -1086,15 +1103,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B1" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -1102,7 +1119,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B3" t="n">
         <v>6</v>
@@ -1110,7 +1127,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -1118,7 +1135,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B5" t="n">
         <v>5</v>
@@ -1126,7 +1143,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B6" t="n">
         <v>5</v>
@@ -1134,7 +1151,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
@@ -1142,7 +1159,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B8" t="n">
         <v>4</v>
@@ -1150,7 +1167,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B9" t="n">
         <v>19</v>
@@ -1158,7 +1175,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B10" t="n">
         <v>10</v>
@@ -1166,7 +1183,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B11" t="n">
         <v>13</v>
@@ -1174,7 +1191,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B12" t="n">
         <v>18</v>
@@ -1182,7 +1199,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B13" t="n">
         <v>28</v>
@@ -1190,7 +1207,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B14" t="n">
         <v>12</v>
@@ -1198,7 +1215,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B15" t="n">
         <v>22</v>
@@ -1206,7 +1223,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B16" t="n">
         <v>2</v>
@@ -1214,7 +1231,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B17" t="n">
         <v>0</v>
@@ -1222,7 +1239,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B18" t="n">
         <v>2</v>
@@ -1230,7 +1247,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B19" t="n">
         <v>0</v>
@@ -1238,7 +1255,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B20" t="n">
         <v>2</v>
@@ -1246,7 +1263,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B21" t="n">
         <v>9.31578947368421</v>
@@ -1265,15 +1282,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B2" t="n">
         <v>29</v>
@@ -1281,7 +1298,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B3" t="n">
         <v>29</v>
@@ -1289,7 +1306,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B4" t="n">
         <v>24</v>
@@ -1297,7 +1314,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B5" t="n">
         <v>23</v>
@@ -1305,7 +1322,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B6" t="n">
         <v>26</v>
@@ -1313,7 +1330,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B7" t="n">
         <v>26</v>
@@ -1321,7 +1338,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B8" t="n">
         <v>20</v>
@@ -1329,7 +1346,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B9" t="n">
         <v>22</v>
@@ -1337,7 +1354,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B10" t="n">
         <v>28</v>
@@ -1345,7 +1362,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B11" t="n">
         <v>21</v>
@@ -1353,7 +1370,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B12" t="n">
         <v>24</v>
@@ -1361,7 +1378,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B13" t="n">
         <v>20</v>
@@ -1369,7 +1386,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B14" t="n">
         <v>21</v>
@@ -1377,7 +1394,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B15" t="n">
         <v>20</v>
@@ -1385,15 +1402,15 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B17" t="n">
         <v>23.5</v>
@@ -1412,33 +1429,33 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E2" t="n">
         <v>0.14</v>
@@ -1446,16 +1463,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C3" t="n">
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E3" t="n">
         <v>0.02</v>
@@ -1463,33 +1480,33 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" t="s">
         <v>67</v>
       </c>
-      <c r="B4" t="s">
-        <v>65</v>
-      </c>
       <c r="C4" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D4" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E5" t="n">
         <v>0.02</v>
@@ -1497,33 +1514,33 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C6" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D6" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E6" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" t="s">
         <v>68</v>
-      </c>
-      <c r="B7" t="s">
-        <v>66</v>
       </c>
       <c r="C7" t="n">
         <v>20</v>
       </c>
       <c r="D7" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E7" t="n">
         <v>0.12</v>
@@ -1531,16 +1548,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E8" t="n">
         <v>0.04</v>
@@ -1548,16 +1565,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E9" t="n">
         <v>0.03</v>
@@ -1565,16 +1582,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
         <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E10" t="n">
         <v>0.15</v>
@@ -1582,16 +1599,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C11" t="n">
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E11" t="n">
         <v>0.02</v>
@@ -1599,16 +1616,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C12" t="n">
         <v>63</v>
       </c>
       <c r="D12" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E12" t="n">
         <v>0.37</v>
@@ -1616,103 +1633,120 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E13" t="n">
-        <v>0.38</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E14" t="n">
-        <v>0.02</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B15" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C15" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E15" t="n">
-        <v>0.09</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D16" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E16" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B17" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C17" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E17" t="n">
-        <v>0.14</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B18" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C18" t="n">
+        <v>24</v>
+      </c>
+      <c r="D18" t="n">
+        <v>170</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>76</v>
+      </c>
+      <c r="B19" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" t="n">
         <v>13</v>
       </c>
-      <c r="D18" t="n">
-        <v>169</v>
-      </c>
-      <c r="E18" t="n">
+      <c r="D19" t="n">
+        <v>170</v>
+      </c>
+      <c r="E19" t="n">
         <v>0.08</v>
       </c>
     </row>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/coalitions.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/coalitions.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
   <si>
     <t xml:space="preserve">majority_sorted</t>
   </si>
@@ -34,16 +34,22 @@
     <t xml:space="preserve">Lackey; Advocate Christ Medical; Diamond;  R.J. Reynolds </t>
   </si>
   <si>
+    <t xml:space="preserve">Roberts, Alito, Thomas, Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Miller; Parrish; Zuch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts, Alito, Thomas, Gorsuch, Kavanaugh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SF v. EPA; Trump v. J.G.G.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Roberts, Alito, Thomas, Gorsuch, Kavanaugh, Barrett</t>
   </si>
   <si>
-    <t xml:space="preserve">Trump v. J.G.G.; Skrmetti; McLaughlin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts, Alito, Thomas, Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Miller; Parrish; Zuch</t>
+    <t xml:space="preserve">Skrmetti; McLaughlin</t>
   </si>
   <si>
     <t xml:space="preserve">Roberts, Alito, Thomas, Sotomayor, Kagan, Kavanaugh, Barrett</t>
@@ -64,64 +70,64 @@
     <t xml:space="preserve">Vanderstok; A.A.R.P v. Trump</t>
   </si>
   <si>
+    <t xml:space="preserve">Roberts, Sotomayor, Kagan, Kavanaugh, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Williams; Glossip</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Drummond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito, Thomas, Gorsuch, Kavanaugh, Barrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOE v. CA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alito, Thomas, Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calumet </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts, Alito, Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andrew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts, Alito, Thomas, Sotomayor, Kagan, Gorsuch, Barrett, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laboratory Corp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts, Alito, Thomas, Sotomayor, Kagan, Gorsuch, Kavanaugh, Barrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stanley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts, Alito, Thomas, Sotomayor, Kagan, Gorsuch, Kavanaugh, Barrett, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seven County</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roberts, Sotomayor, Gorsuch, Kavanaugh, Barrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feliciano</t>
+  </si>
+  <si>
     <t xml:space="preserve">Roberts, Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
   </si>
   <si>
-    <t xml:space="preserve">Glossip; NRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Drummond</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alito, Thomas, Gorsuch, Kavanaugh, Barrett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DOE v. CA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alito, Thomas, Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calumet </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts, Alito, Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Andrew</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts, Alito, Thomas, Sotomayor, Kagan, Gorsuch, Barrett, Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laboratory Corp.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts, Alito, Thomas, Sotomayor, Kagan, Gorsuch, Kavanaugh, Barrett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stanley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts, Alito, Thomas, Sotomayor, Kagan, Gorsuch, Kavanaugh, Barrett, Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seven County</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts, Sotomayor, Gorsuch, Kavanaugh, Barrett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feliciano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts, Sotomayor, Kagan, Kavanaugh, Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Willaims</t>
+    <t xml:space="preserve">NRC</t>
   </si>
   <si>
     <t xml:space="preserve">Roberts, Thomas, Sotomayor, Kagan, Gorsuch, Kavanaugh, Barrett, Jackson</t>
@@ -614,7 +620,7 @@
         <v>7</v>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
@@ -669,7 +675,7 @@
         <v>17</v>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
@@ -794,6 +800,17 @@
       </c>
       <c r="C20" t="s">
         <v>40</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -809,7 +826,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -817,7 +834,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B2" t="n">
         <v>28</v>
@@ -825,7 +842,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B3" t="n">
         <v>31</v>
@@ -833,7 +850,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B4" t="n">
         <v>31</v>
@@ -841,7 +858,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B5" t="n">
         <v>20</v>
@@ -849,7 +866,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B6" t="n">
         <v>30</v>
@@ -857,7 +874,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B7" t="n">
         <v>27</v>
@@ -865,7 +882,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B8" t="n">
         <v>18</v>
@@ -873,7 +890,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B9" t="n">
         <v>26</v>
@@ -881,7 +898,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B10" t="n">
         <v>31</v>
@@ -889,7 +906,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B11" t="n">
         <v>19</v>
@@ -897,7 +914,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B12" t="n">
         <v>24</v>
@@ -905,7 +922,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B13" t="n">
         <v>31</v>
@@ -913,7 +930,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B14" t="n">
         <v>18</v>
@@ -921,7 +938,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B15" t="n">
         <v>26</v>
@@ -929,18 +946,18 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B17" t="n">
-        <v>24.7333333333333</v>
+        <v>24.8</v>
       </c>
     </row>
   </sheetData>
@@ -956,15 +973,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B2" t="n">
         <v>33</v>
@@ -972,7 +989,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B3" t="n">
         <v>40</v>
@@ -980,7 +997,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B4" t="n">
         <v>39</v>
@@ -988,7 +1005,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B5" t="n">
         <v>27</v>
@@ -996,7 +1013,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B6" t="n">
         <v>41</v>
@@ -1004,7 +1021,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B7" t="n">
         <v>33</v>
@@ -1012,7 +1029,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B8" t="n">
         <v>26</v>
@@ -1020,7 +1037,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B9" t="n">
         <v>34</v>
@@ -1028,7 +1045,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B10" t="n">
         <v>42</v>
@@ -1036,7 +1053,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B11" t="n">
         <v>32</v>
@@ -1044,7 +1061,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B12" t="n">
         <v>37</v>
@@ -1052,7 +1069,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B13" t="n">
         <v>48</v>
@@ -1060,7 +1077,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B14" t="n">
         <v>31</v>
@@ -1068,7 +1085,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B15" t="n">
         <v>44</v>
@@ -1076,18 +1093,18 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B17" t="n">
-        <v>35.0666666666667</v>
+        <v>35.2</v>
       </c>
     </row>
   </sheetData>
@@ -1103,15 +1120,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -1119,7 +1136,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B3" t="n">
         <v>6</v>
@@ -1127,7 +1144,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -1135,7 +1152,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B5" t="n">
         <v>5</v>
@@ -1143,7 +1160,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B6" t="n">
         <v>5</v>
@@ -1151,7 +1168,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
@@ -1159,7 +1176,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B8" t="n">
         <v>4</v>
@@ -1167,7 +1184,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B9" t="n">
         <v>19</v>
@@ -1175,7 +1192,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B10" t="n">
         <v>10</v>
@@ -1183,7 +1200,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B11" t="n">
         <v>13</v>
@@ -1191,7 +1208,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B12" t="n">
         <v>18</v>
@@ -1199,7 +1216,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B13" t="n">
         <v>28</v>
@@ -1207,7 +1224,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B14" t="n">
         <v>12</v>
@@ -1215,7 +1232,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B15" t="n">
         <v>22</v>
@@ -1223,7 +1240,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B16" t="n">
         <v>2</v>
@@ -1231,7 +1248,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B17" t="n">
         <v>0</v>
@@ -1239,7 +1256,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B18" t="n">
         <v>2</v>
@@ -1247,26 +1264,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>56</v>
-      </c>
-      <c r="B20" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>57</v>
-      </c>
-      <c r="B21" t="n">
-        <v>9.31578947368421</v>
+        <v>10.2941176470588</v>
       </c>
     </row>
   </sheetData>
@@ -1282,15 +1283,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B2" t="n">
         <v>29</v>
@@ -1298,7 +1299,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B3" t="n">
         <v>29</v>
@@ -1306,7 +1307,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B4" t="n">
         <v>24</v>
@@ -1314,7 +1315,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B5" t="n">
         <v>23</v>
@@ -1322,7 +1323,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B6" t="n">
         <v>26</v>
@@ -1330,7 +1331,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B7" t="n">
         <v>26</v>
@@ -1338,7 +1339,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B8" t="n">
         <v>20</v>
@@ -1346,7 +1347,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B9" t="n">
         <v>22</v>
@@ -1354,7 +1355,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B10" t="n">
         <v>28</v>
@@ -1362,7 +1363,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B11" t="n">
         <v>21</v>
@@ -1370,7 +1371,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B12" t="n">
         <v>24</v>
@@ -1378,7 +1379,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B13" t="n">
         <v>20</v>
@@ -1386,7 +1387,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B14" t="n">
         <v>21</v>
@@ -1394,7 +1395,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B15" t="n">
         <v>20</v>
@@ -1402,15 +1403,15 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B17" t="n">
         <v>23.5</v>
@@ -1429,33 +1430,33 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C2" t="n">
         <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E2" t="n">
         <v>0.14</v>
@@ -1463,16 +1464,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C3" t="n">
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E3" t="n">
         <v>0.02</v>
@@ -1480,16 +1481,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" t="s">
         <v>69</v>
       </c>
-      <c r="B4" t="s">
-        <v>67</v>
-      </c>
       <c r="C4" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D4" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E4" t="n">
         <v>0.31</v>
@@ -1497,33 +1498,33 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C6" t="n">
         <v>39</v>
       </c>
       <c r="D6" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E6" t="n">
         <v>0.23</v>
@@ -1531,16 +1532,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" t="s">
         <v>70</v>
-      </c>
-      <c r="B7" t="s">
-        <v>68</v>
       </c>
       <c r="C7" t="n">
         <v>20</v>
       </c>
       <c r="D7" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E7" t="n">
         <v>0.12</v>
@@ -1548,16 +1549,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C8" t="n">
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E8" t="n">
         <v>0.04</v>
@@ -1565,16 +1566,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E9" t="n">
         <v>0.03</v>
@@ -1582,16 +1583,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C10" t="n">
         <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E10" t="n">
         <v>0.15</v>
@@ -1599,16 +1600,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C11" t="n">
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E11" t="n">
         <v>0.02</v>
@@ -1616,16 +1617,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C12" t="n">
         <v>63</v>
       </c>
       <c r="D12" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E12" t="n">
         <v>0.37</v>
@@ -1633,16 +1634,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E13" t="n">
         <v>0.01</v>
@@ -1650,16 +1651,16 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C14" t="n">
         <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E14" t="n">
         <v>0.38</v>
@@ -1667,16 +1668,16 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C15" t="n">
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E15" t="n">
         <v>0.02</v>
@@ -1684,16 +1685,16 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C16" t="n">
         <v>15</v>
       </c>
       <c r="D16" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E16" t="n">
         <v>0.09</v>
@@ -1701,16 +1702,16 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E17" t="n">
         <v>0.04</v>
@@ -1718,16 +1719,16 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C18" t="n">
         <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E18" t="n">
         <v>0.14</v>
@@ -1735,16 +1736,16 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B19" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C19" t="n">
         <v>13</v>
       </c>
       <c r="D19" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E19" t="n">
         <v>0.08</v>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/coalitions.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/coalitions.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="81">
   <si>
     <t xml:space="preserve">majority_sorted</t>
   </si>
@@ -34,42 +34,48 @@
     <t xml:space="preserve">Lackey; Advocate Christ Medical; Diamond;  R.J. Reynolds </t>
   </si>
   <si>
+    <t xml:space="preserve">Roberts, Alito, Thomas, Gorsuch, Kavanaugh, Barrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skrmetti; McLaughlin; Medina</t>
+  </si>
+  <si>
     <t xml:space="preserve">Roberts, Alito, Thomas, Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
   </si>
   <si>
     <t xml:space="preserve">Miller; Parrish; Zuch</t>
   </si>
   <si>
+    <t xml:space="preserve">Roberts, Sotomayor, Kagan, Gorsuch, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Velazquez; Perttu; Hewitt</t>
+  </si>
+  <si>
     <t xml:space="preserve">Roberts, Alito, Thomas, Gorsuch, Kavanaugh</t>
   </si>
   <si>
     <t xml:space="preserve">SF v. EPA; Trump v. J.G.G.</t>
   </si>
   <si>
-    <t xml:space="preserve">Roberts, Alito, Thomas, Gorsuch, Kavanaugh, Barrett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skrmetti; McLaughlin</t>
-  </si>
-  <si>
     <t xml:space="preserve">Roberts, Alito, Thomas, Sotomayor, Kagan, Kavanaugh, Barrett</t>
   </si>
   <si>
     <t xml:space="preserve">Bufkin; Delligatti</t>
   </si>
   <si>
-    <t xml:space="preserve">Roberts, Sotomayor, Kagan, Gorsuch, Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Velazquez; Perttu</t>
-  </si>
-  <si>
     <t xml:space="preserve">Roberts, Sotomayor, Kagan, Gorsuch, Kavanaugh, Barrett, Jackson</t>
   </si>
   <si>
     <t xml:space="preserve">Vanderstok; A.A.R.P v. Trump</t>
   </si>
   <si>
+    <t xml:space="preserve">Roberts, Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NRC; Guitierrez</t>
+  </si>
+  <si>
     <t xml:space="preserve">Roberts, Sotomayor, Kagan, Kavanaugh, Jackson</t>
   </si>
   <si>
@@ -100,6 +106,12 @@
     <t xml:space="preserve">Andrew</t>
   </si>
   <si>
+    <t xml:space="preserve">Roberts, Alito, Thomas, Kavanaugh, Barrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riley</t>
+  </si>
+  <si>
     <t xml:space="preserve">Roberts, Alito, Thomas, Sotomayor, Kagan, Gorsuch, Barrett, Jackson</t>
   </si>
   <si>
@@ -122,12 +134,6 @@
   </si>
   <si>
     <t xml:space="preserve">Feliciano</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts, Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NRC</t>
   </si>
   <si>
     <t xml:space="preserve">Roberts, Thomas, Sotomayor, Kagan, Gorsuch, Kavanaugh, Barrett, Jackson</t>
@@ -620,7 +626,7 @@
         <v>7</v>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
@@ -631,7 +637,7 @@
         <v>9</v>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -686,7 +692,7 @@
         <v>19</v>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="s">
         <v>20</v>
@@ -811,6 +817,17 @@
       </c>
       <c r="C21" t="s">
         <v>42</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -826,7 +843,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -834,7 +851,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B2" t="n">
         <v>28</v>
@@ -842,7 +859,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B3" t="n">
         <v>31</v>
@@ -850,7 +867,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B4" t="n">
         <v>31</v>
@@ -858,7 +875,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B5" t="n">
         <v>20</v>
@@ -866,7 +883,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B6" t="n">
         <v>30</v>
@@ -874,7 +891,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B7" t="n">
         <v>27</v>
@@ -882,7 +899,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B8" t="n">
         <v>18</v>
@@ -890,7 +907,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B9" t="n">
         <v>26</v>
@@ -898,7 +915,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B10" t="n">
         <v>31</v>
@@ -906,7 +923,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B11" t="n">
         <v>19</v>
@@ -914,7 +931,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B12" t="n">
         <v>24</v>
@@ -922,7 +939,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B13" t="n">
         <v>31</v>
@@ -930,7 +947,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B14" t="n">
         <v>18</v>
@@ -938,7 +955,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B15" t="n">
         <v>26</v>
@@ -946,18 +963,18 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B17" t="n">
-        <v>24.8</v>
+        <v>25.0666666666667</v>
       </c>
     </row>
   </sheetData>
@@ -973,15 +990,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B2" t="n">
         <v>33</v>
@@ -989,7 +1006,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B3" t="n">
         <v>40</v>
@@ -997,7 +1014,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B4" t="n">
         <v>39</v>
@@ -1005,7 +1022,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B5" t="n">
         <v>27</v>
@@ -1013,7 +1030,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B6" t="n">
         <v>41</v>
@@ -1021,7 +1038,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B7" t="n">
         <v>33</v>
@@ -1029,7 +1046,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B8" t="n">
         <v>26</v>
@@ -1037,7 +1054,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B9" t="n">
         <v>34</v>
@@ -1045,7 +1062,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B10" t="n">
         <v>42</v>
@@ -1053,7 +1070,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B11" t="n">
         <v>32</v>
@@ -1061,7 +1078,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B12" t="n">
         <v>37</v>
@@ -1069,7 +1086,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B13" t="n">
         <v>48</v>
@@ -1077,7 +1094,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B14" t="n">
         <v>31</v>
@@ -1085,7 +1102,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B15" t="n">
         <v>44</v>
@@ -1093,18 +1110,18 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B16" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B17" t="n">
-        <v>35.2</v>
+        <v>35.5333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -1120,15 +1137,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B2" t="n">
         <v>14</v>
@@ -1136,7 +1153,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B3" t="n">
         <v>6</v>
@@ -1144,7 +1161,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B4" t="n">
         <v>14</v>
@@ -1152,7 +1169,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B5" t="n">
         <v>5</v>
@@ -1160,7 +1177,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B6" t="n">
         <v>5</v>
@@ -1168,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
@@ -1176,7 +1193,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B8" t="n">
         <v>4</v>
@@ -1184,7 +1201,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B9" t="n">
         <v>19</v>
@@ -1192,7 +1209,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B10" t="n">
         <v>10</v>
@@ -1200,7 +1217,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B11" t="n">
         <v>13</v>
@@ -1208,7 +1225,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B12" t="n">
         <v>18</v>
@@ -1216,7 +1233,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B13" t="n">
         <v>28</v>
@@ -1224,7 +1241,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B14" t="n">
         <v>12</v>
@@ -1232,7 +1249,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B15" t="n">
         <v>22</v>
@@ -1240,7 +1257,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B16" t="n">
         <v>2</v>
@@ -1248,7 +1265,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B17" t="n">
         <v>0</v>
@@ -1256,7 +1273,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B18" t="n">
         <v>2</v>
@@ -1264,10 +1281,26 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B19" t="n">
-        <v>10.2941176470588</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" t="n">
+        <v>9.31578947368421</v>
       </c>
     </row>
   </sheetData>
@@ -1283,15 +1316,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B2" t="n">
         <v>29</v>
@@ -1299,7 +1332,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B3" t="n">
         <v>29</v>
@@ -1307,7 +1340,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B4" t="n">
         <v>24</v>
@@ -1315,7 +1348,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B5" t="n">
         <v>23</v>
@@ -1323,7 +1356,7 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B6" t="n">
         <v>26</v>
@@ -1331,7 +1364,7 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B7" t="n">
         <v>26</v>
@@ -1339,7 +1372,7 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B8" t="n">
         <v>20</v>
@@ -1347,7 +1380,7 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B9" t="n">
         <v>22</v>
@@ -1355,7 +1388,7 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B10" t="n">
         <v>28</v>
@@ -1363,7 +1396,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B11" t="n">
         <v>21</v>
@@ -1371,7 +1404,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B12" t="n">
         <v>24</v>
@@ -1379,7 +1412,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B13" t="n">
         <v>20</v>
@@ -1387,7 +1420,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B14" t="n">
         <v>21</v>
@@ -1395,7 +1428,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B15" t="n">
         <v>20</v>
@@ -1403,15 +1436,15 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B17" t="n">
         <v>23.5</v>
@@ -1430,33 +1463,33 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C2" t="n">
         <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E2" t="n">
         <v>0.14</v>
@@ -1464,16 +1497,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C3" t="n">
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E3" t="n">
         <v>0.02</v>
@@ -1481,16 +1514,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B4" t="s">
         <v>71</v>
       </c>
-      <c r="B4" t="s">
-        <v>69</v>
-      </c>
       <c r="C4" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D4" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E4" t="n">
         <v>0.31</v>
@@ -1498,16 +1531,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C5" t="n">
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E5" t="n">
         <v>0.03</v>
@@ -1515,16 +1548,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C6" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D6" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E6" t="n">
         <v>0.23</v>
@@ -1532,16 +1565,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" t="s">
         <v>72</v>
       </c>
-      <c r="B7" t="s">
-        <v>70</v>
-      </c>
       <c r="C7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E7" t="n">
         <v>0.12</v>
@@ -1549,16 +1582,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E8" t="n">
         <v>0.04</v>
@@ -1566,16 +1599,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E9" t="n">
         <v>0.03</v>
@@ -1583,16 +1616,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
         <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E10" t="n">
         <v>0.15</v>
@@ -1600,16 +1633,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C11" t="n">
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E11" t="n">
         <v>0.02</v>
@@ -1617,16 +1650,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D12" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E12" t="n">
         <v>0.37</v>
@@ -1634,16 +1667,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E13" t="n">
         <v>0.01</v>
@@ -1651,16 +1684,16 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B14" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E14" t="n">
         <v>0.38</v>
@@ -1668,16 +1701,16 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C15" t="n">
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E15" t="n">
         <v>0.02</v>
@@ -1685,16 +1718,16 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C16" t="n">
         <v>15</v>
       </c>
       <c r="D16" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E16" t="n">
         <v>0.09</v>
@@ -1702,16 +1735,16 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E17" t="n">
         <v>0.04</v>
@@ -1719,16 +1752,16 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B18" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C18" t="n">
         <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E18" t="n">
         <v>0.14</v>
@@ -1736,19 +1769,19 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C19" t="n">
         <v>13</v>
       </c>
       <c r="D19" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="E19" t="n">
-        <v>0.08</v>
+        <v>0.07</v>
       </c>
     </row>
   </sheetData>

--- a/Stat Reviews/OT24_StatReview/scotusblog_replication/data/coalitions.xlsx
+++ b/Stat Reviews/OT24_StatReview/scotusblog_replication/data/coalitions.xlsx
@@ -28,16 +28,22 @@
     <t xml:space="preserve">case</t>
   </si>
   <si>
+    <t xml:space="preserve">Roberts, Alito, Thomas, Gorsuch, Kavanaugh, Barrett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skrmetti; McLaughlin; Medina; Trump v. CASA; Mahmoud; Free Speech</t>
+  </si>
+  <si>
     <t xml:space="preserve">Roberts, Alito, Thomas, Kagan, Gorsuch, Kavanaugh, Barrett</t>
   </si>
   <si>
     <t xml:space="preserve">Lackey; Advocate Christ Medical; Diamond;  R.J. Reynolds </t>
   </si>
   <si>
-    <t xml:space="preserve">Roberts, Alito, Thomas, Gorsuch, Kavanaugh, Barrett</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skrmetti; McLaughlin; Medina</t>
+    <t xml:space="preserve">Roberts, Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NRC; Guitierrez; Kennedy; Consumers' Research</t>
   </si>
   <si>
     <t xml:space="preserve">Roberts, Alito, Thomas, Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
@@ -68,12 +74,6 @@
   </si>
   <si>
     <t xml:space="preserve">Vanderstok; A.A.R.P v. Trump</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roberts, Sotomayor, Kagan, Kavanaugh, Barrett, Jackson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NRC; Guitierrez</t>
   </si>
   <si>
     <t xml:space="preserve">Roberts, Sotomayor, Kagan, Kavanaugh, Jackson</t>
@@ -604,7 +604,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -615,7 +615,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -626,7 +626,7 @@
         <v>7</v>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
@@ -648,7 +648,7 @@
         <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
         <v>12</v>
@@ -966,7 +966,7 @@
         <v>60</v>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -974,7 +974,7 @@
         <v>61</v>
       </c>
       <c r="B17" t="n">
-        <v>25.0666666666667</v>
+        <v>25.4</v>
       </c>
     </row>
   </sheetData>
@@ -1113,7 +1113,7 @@
         <v>60</v>
       </c>
       <c r="B16" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17">
@@ -1121,7 +1121,7 @@
         <v>61</v>
       </c>
       <c r="B17" t="n">
-        <v>35.5333333333333</v>
+        <v>35.9333333333333</v>
       </c>
     </row>
   </sheetData>
@@ -1297,10 +1297,50 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>60</v>
+      </c>
+      <c r="B24" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
         <v>61</v>
       </c>
-      <c r="B21" t="n">
-        <v>9.31578947368421</v>
+      <c r="B26" t="n">
+        <v>7.625</v>
       </c>
     </row>
   </sheetData>
@@ -1489,10 +1529,10 @@
         <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="E2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="3">
@@ -1506,7 +1546,7 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="E3" t="n">
         <v>0.02</v>
@@ -1520,10 +1560,10 @@
         <v>71</v>
       </c>
       <c r="C4" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D4" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="E4" t="n">
         <v>0.31</v>
@@ -1540,7 +1580,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="E5" t="n">
         <v>0.03</v>
@@ -1557,7 +1597,7 @@
         <v>41</v>
       </c>
       <c r="D6" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="E6" t="n">
         <v>0.23</v>
@@ -1574,7 +1614,7 @@
         <v>21</v>
       </c>
       <c r="D7" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="E7" t="n">
         <v>0.12</v>
@@ -1591,7 +1631,7 @@
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="E8" t="n">
         <v>0.04</v>
@@ -1608,7 +1648,7 @@
         <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="E9" t="n">
         <v>0.03</v>
@@ -1625,10 +1665,10 @@
         <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="E10" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="11">
@@ -1642,7 +1682,7 @@
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="E11" t="n">
         <v>0.02</v>
@@ -1656,10 +1696,10 @@
         <v>71</v>
       </c>
       <c r="C12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D12" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="E12" t="n">
         <v>0.37</v>
@@ -1676,7 +1716,7 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="E13" t="n">
         <v>0.01</v>
@@ -1690,10 +1730,10 @@
         <v>71</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="E14" t="n">
         <v>0.38</v>
@@ -1710,7 +1750,7 @@
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="E15" t="n">
         <v>0.02</v>
@@ -1727,10 +1767,10 @@
         <v>15</v>
       </c>
       <c r="D16" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="E16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="17">
@@ -1744,7 +1784,7 @@
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="E17" t="n">
         <v>0.04</v>
@@ -1761,10 +1801,10 @@
         <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="E18" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="19">
@@ -1778,7 +1818,7 @@
         <v>13</v>
       </c>
       <c r="D19" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="E19" t="n">
         <v>0.07</v>
